--- a/362/food/2026-01-20-sm.xlsx
+++ b/362/food/2026-01-20-sm.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -46,7 +46,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -82,19 +82,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -305,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -313,17 +300,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -335,82 +325,70 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -802,19 +780,19 @@
           <t>Школа</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>СОШ № 12</t>
         </is>
       </c>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="37" t="n"/>
+      <c r="C1" s="33" t="n"/>
+      <c r="D1" s="34" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Отд./корп</t>
         </is>
       </c>
-      <c r="F1" s="3" t="n"/>
+      <c r="F1" s="32" t="n"/>
       <c r="G1" s="4" t="n"/>
       <c r="I1" s="2" t="inlineStr">
         <is>
@@ -890,183 +868,183 @@
           <t>Завтрак</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Сырники из творога запеченые</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="15" t="n">
         <v>27.53</v>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="14" t="n">
         <v>195</v>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="16" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="21" t="n"/>
-      <c r="J5" s="22" t="n"/>
+      <c r="A5" s="17" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="21" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="18" t="n"/>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>гор.напиток</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Чай с молоком или сливками</t>
         </is>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="22" t="n">
         <v>200</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="23" t="n">
         <v>36.71</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="24" t="n">
         <v>83.8</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="24" t="n">
         <v>1.4</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="25" t="n">
         <v>15.9</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>878</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
         </is>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="23" t="n">
         <v>9.18</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="24" t="n">
         <v>116.8</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="24" t="n">
         <v>3.9</v>
       </c>
-      <c r="I7" s="25" t="n">
+      <c r="I7" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="26" t="n">
+      <c r="J7" s="25" t="n">
         <v>24.1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>фрукты</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Яблоко</t>
         </is>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="23" t="n">
         <v>18.35</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="24" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="24" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="25" t="n">
+      <c r="I8" s="24" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="25" t="n">
         <v>16.8</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="22" t="n"/>
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="21" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="18" t="n"/>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="22" t="n"/>
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="21" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -1074,139 +1052,139 @@
           <t>Обед</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>закуска</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="28" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="26" t="n"/>
+      <c r="J11" s="27" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="18" t="n"/>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="22" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="18" t="n"/>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="22" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="21" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>гарнир</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="22" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="21" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="18" t="n"/>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="22" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="18" t="n"/>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>хлеб бел.</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="22" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="21" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="18" t="n"/>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>хлеб черн.</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="22" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="21" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="18" t="n"/>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="22" t="n"/>
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="21" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="31" t="n"/>
-      <c r="H19" s="31" t="n"/>
-      <c r="I19" s="31" t="n"/>
-      <c r="J19" s="32" t="n"/>
+      <c r="A19" s="28" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="30" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+      <c r="H19" s="30" t="n"/>
+      <c r="I19" s="30" t="n"/>
+      <c r="J19" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
